--- a/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
+++ b/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
@@ -1168,34 +1168,34 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K12"/>
+  <x:dimension ref="A1:G9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="11" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="6" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:11">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11">
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:11">
+    <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:11"/>
-    <x:row r="9" spans="1:11"/>
+    <x:row r="7" spans="1:7"/>
+    <x:row r="9" spans="1:7"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1211,14 +1211,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E5"/>
+  <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="5" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="1:5"/>
-    <x:row r="4" spans="1:5"/>
+    <x:row r="2" spans="1:1"/>
+    <x:row r="4" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1234,13 +1231,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D4"/>
+  <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4"/>
+    <x:row r="1" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1256,21 +1250,20 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D7"/>
+  <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="23.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="4" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:4"/>
-    <x:row r="3" spans="1:4"/>
-    <x:row r="4" spans="1:4"/>
+    <x:row r="2" spans="1:1"/>
+    <x:row r="3" spans="1:1"/>
+    <x:row r="4" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1286,13 +1279,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E9"/>
+  <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultColWidth="10.710625" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="5" width="10.710625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5"/>
+    <x:row r="1" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1308,13 +1298,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D5"/>
+  <x:dimension ref="A1:A2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="1:4"/>
+    <x:row r="2" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1330,15 +1317,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I11"/>
+  <x:dimension ref="A1:F8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="9" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9"/>
-    <x:row r="3" spans="1:9"/>
-    <x:row r="8" spans="1:9"/>
+    <x:row r="1" spans="1:6"/>
+    <x:row r="3" spans="1:6"/>
+    <x:row r="8" spans="1:6"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1354,13 +1338,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D5"/>
+  <x:dimension ref="A1:A2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="1:4"/>
+    <x:row r="2" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1376,13 +1357,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D9"/>
+  <x:dimension ref="A1:A2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="1:4"/>
+    <x:row r="2" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1398,15 +1376,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D6"/>
+  <x:dimension ref="A1:A3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4"/>
-    <x:row r="2" spans="1:4"/>
-    <x:row r="3" spans="1:4"/>
+    <x:row r="1" spans="1:1"/>
+    <x:row r="2" spans="1:1"/>
+    <x:row r="3" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1422,13 +1397,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D4"/>
+  <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4"/>
+    <x:row r="1" spans="1:1"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
+++ b/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
@@ -1165,99 +1165,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:G9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="6" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7"/>
     <x:row r="9" spans="1:7"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId16"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="2" spans="1:1"/>
     <x:row r="4" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId34"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId36"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23.853482" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -1265,58 +1241,37 @@
     <x:row r="3" spans="1:1"/>
     <x:row r="4" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId18"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultColWidth="10.710625" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId20"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="2" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId22"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1324,58 +1279,37 @@
     <x:row r="3" spans="1:6"/>
     <x:row r="8" spans="1:6"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId24"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="2" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId26"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="2" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId28"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -1383,30 +1317,19 @@
     <x:row r="2" spans="1:1"/>
     <x:row r="3" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId30"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1"/>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing r:id="rId32"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
+++ b/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
@@ -1229,7 +1229,7 @@
   <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23.853482" customWidth="1"/>
+    <x:col min="1" max="1" width="23.139196" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">

--- a/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
+++ b/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
@@ -1168,7 +1168,7 @@
   <x:dimension ref="A1:G9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="6" width="9.140625"/>
+    <x:col min="1" max="6" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -1229,7 +1229,7 @@
   <x:dimension ref="A1:A4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23.139196" customWidth="1"/>
+    <x:col min="1" max="1" width="23.142857" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
@@ -1249,7 +1249,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:dimension ref="A1:A1"/>
-  <x:sheetFormatPr defaultColWidth="10.710625" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="10.714286" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1"/>
   </x:sheetData>
